--- a/data/trans_orig/P74B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P74B-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2007</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3934</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>60,96%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>983</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3857</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5103</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>59,77%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>983</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4232</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32049</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36238</t>
+          <t>35367</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>158498</t>
+          <t>157605</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>166941</t>
+          <t>166954</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170899</t>
+          <t>170451</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179533</t>
+          <t>179537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24171</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>254824</t>
+          <t>255720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25815</t>
+          <t>25598</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>283648</t>
+          <t>284171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>299088</t>
+          <t>299445</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42231</t>
+          <t>41316</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56715</t>
+          <t>56770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>42495</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70256</t>
+          <t>71097</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>276978</t>
+          <t>278007</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>287815</t>
+          <t>287956</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27296</t>
+          <t>28211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289734</t>
+          <t>288893</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>316869</t>
+          <t>317495</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14823</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33300</t>
+          <t>33465</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>137902</t>
+          <t>137398</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154856</t>
+          <t>154797</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149235</t>
+          <t>151595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>191719</t>
+          <t>191645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>245739</t>
+          <t>245574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264216</t>
+          <t>264326</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30309</t>
+          <t>30813</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255532</t>
+          <t>255606</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>298016</t>
+          <t>295656</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34625</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59100</t>
+          <t>58344</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>183472</t>
+          <t>183346</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194778</t>
+          <t>194716</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>216993</t>
+          <t>216372</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>256737</t>
+          <t>255653</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182675</t>
+          <t>183431</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207150</t>
+          <t>207183</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>183555</t>
+          <t>184639</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>223299</t>
+          <t>223920</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18859</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37132</t>
+          <t>37663</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>97589</t>
+          <t>96476</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109035</t>
+          <t>109006</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>115376</t>
+          <t>115867</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>148140</t>
+          <t>146875</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103959</t>
+          <t>103428</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122232</t>
+          <t>122302</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12629</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>103168</t>
+          <t>104433</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>135932</t>
+          <t>135441</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87757</t>
+          <t>87341</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128470</t>
+          <t>128270</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>488369</t>
+          <t>487602</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>524803</t>
+          <t>524709</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>574679</t>
+          <t>573623</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>654034</t>
+          <t>658317</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1287042</t>
+          <t>1287242</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1327755</t>
+          <t>1328171</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>87273</t>
+          <t>87367</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123707</t>
+          <t>124474</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1373554</t>
+          <t>1369271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1452909</t>
+          <t>1453965</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2012</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2012 (tasa de respuesta: 97,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19667</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>41397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29806</t>
+          <t>29429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12896</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33066</t>
+          <t>32050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>131640</t>
+          <t>131894</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51441</t>
+          <t>51818</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68287</t>
+          <t>68187</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184944</t>
+          <t>185960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>205114</t>
+          <t>204694</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18014</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31369</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>22492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44631</t>
+          <t>43882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>249321</t>
+          <t>248966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>261629</t>
+          <t>261748</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90658</t>
+          <t>89733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107022</t>
+          <t>107543</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>344731</t>
+          <t>345480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>366265</t>
+          <t>366870</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>17050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45959</t>
+          <t>45843</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70354</t>
+          <t>69891</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>53508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83702</t>
+          <t>86520</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251396</t>
+          <t>251779</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>263867</t>
+          <t>264214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62408</t>
+          <t>62871</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86803</t>
+          <t>86919</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>317889</t>
+          <t>315071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>349354</t>
+          <t>348083</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37199</t>
+          <t>36926</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>183127</t>
+          <t>181543</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204380</t>
+          <t>203450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196171</t>
+          <t>198221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>241823</t>
+          <t>242870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>239732</t>
+          <t>240005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>261763</t>
+          <t>261609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>25419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45742</t>
+          <t>47326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>263978</t>
+          <t>262931</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309630</t>
+          <t>307580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,81%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52099</t>
+          <t>53311</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82048</t>
+          <t>81858</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>179377</t>
+          <t>178761</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>191093</t>
+          <t>191079</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>230849</t>
+          <t>232136</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>272226</t>
+          <t>274117</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>64,06%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151885</t>
+          <t>152075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181834</t>
+          <t>180622</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155661</t>
+          <t>153770</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>197038</t>
+          <t>195751</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47349</t>
+          <t>47139</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72927</t>
+          <t>73458</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135759</t>
+          <t>136735</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>180997</t>
+          <t>183147</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>217057</t>
+          <t>217655</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93891</t>
+          <t>93360</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>119469</t>
+          <t>119679</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>91955</t>
+          <t>91357</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>128015</t>
+          <t>125865</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>148641</t>
+          <t>148660</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>200744</t>
+          <t>199512</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>594825</t>
+          <t>595942</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>651059</t>
+          <t>654384</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>750687</t>
+          <t>753662</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>845000</t>
+          <t>847521</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1174605</t>
+          <t>1175837</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1226708</t>
+          <t>1226689</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>267632</t>
+          <t>264307</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>323866</t>
+          <t>322749</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1449040</t>
+          <t>1446519</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1543353</t>
+          <t>1540378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2016</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2016 (tasa de respuesta: 94,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1715</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11617</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25524</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42238</t>
+          <t>43218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52140</t>
+          <t>52725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>8613</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>142410</t>
+          <t>143856</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154669</t>
+          <t>154631</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36873</t>
+          <t>36928</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47709</t>
+          <t>47370</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184021</t>
+          <t>184900</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199464</t>
+          <t>199753</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21416</t>
+          <t>19995</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31824</t>
+          <t>30512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22254</t>
+          <t>23446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44517</t>
+          <t>46059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228582</t>
+          <t>230003</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244290</t>
+          <t>244275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78267</t>
+          <t>79579</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96076</t>
+          <t>95719</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315572</t>
+          <t>314030</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>337835</t>
+          <t>336643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23898</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28811</t>
+          <t>29360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>51271</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40558</t>
+          <t>39089</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68662</t>
+          <t>67709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>243562</t>
+          <t>244427</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>259674</t>
+          <t>260178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88385</t>
+          <t>86543</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109003</t>
+          <t>108454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>336611</t>
+          <t>337564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364715</t>
+          <t>366184</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14991</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35359</t>
+          <t>34829</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>156327</t>
+          <t>155496</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>180785</t>
+          <t>180841</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>171077</t>
+          <t>170746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>218186</t>
+          <t>213653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>233168</t>
+          <t>233698</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>253536</t>
+          <t>253671</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52617</t>
+          <t>53448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259284</t>
+          <t>263817</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>306393</t>
+          <t>306724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52688</t>
+          <t>54179</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79739</t>
+          <t>81351</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>210641</t>
+          <t>210655</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>261857</t>
+          <t>262114</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>302030</t>
+          <t>301939</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>159048</t>
+          <t>157436</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>186099</t>
+          <t>184608</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>154478</t>
+          <t>154569</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>194651</t>
+          <t>194394</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35758</t>
+          <t>35111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55783</t>
+          <t>55244</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132665</t>
+          <t>131455</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>166581</t>
+          <t>165618</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>198043</t>
+          <t>198284</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,75%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96741</t>
+          <t>97280</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>116766</t>
+          <t>117413</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94632</t>
+          <t>94391</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>126094</t>
+          <t>127057</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>145447</t>
+          <t>147024</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194464</t>
+          <t>194003</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>561515</t>
+          <t>564336</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>621681</t>
+          <t>621389</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>718371</t>
+          <t>720959</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>813686</t>
+          <t>811145</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1163375</t>
+          <t>1163836</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1212392</t>
+          <t>1210815</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>274716</t>
+          <t>275008</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>334882</t>
+          <t>332061</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1440551</t>
+          <t>1443092</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1535866</t>
+          <t>1533278</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P74B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P74B-Edad-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35367</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>157605</t>
+          <t>158049</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>166954</t>
+          <t>166950</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170451</t>
+          <t>169988</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179537</t>
+          <t>179523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20968</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>23945</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>255720</t>
+          <t>255593</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25598</t>
+          <t>25802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284171</t>
+          <t>283874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>299445</t>
+          <t>299565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>13655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41316</t>
+          <t>41209</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56770</t>
+          <t>56731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42495</t>
+          <t>44187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71097</t>
+          <t>71406</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>278007</t>
+          <t>276808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>287956</t>
+          <t>287969</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28211</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>288893</t>
+          <t>288584</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317495</t>
+          <t>315803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>15433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>34854</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>137398</t>
+          <t>137280</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154797</t>
+          <t>154655</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151595</t>
+          <t>148951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>191645</t>
+          <t>191863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,9%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>245574</t>
+          <t>244185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264326</t>
+          <t>263606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13414</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30813</t>
+          <t>30931</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255606</t>
+          <t>255388</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>295656</t>
+          <t>298300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,7%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34592</t>
+          <t>34755</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58344</t>
+          <t>59308</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>183346</t>
+          <t>183914</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194716</t>
+          <t>194889</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>216372</t>
+          <t>216759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>255653</t>
+          <t>255556</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,04%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183431</t>
+          <t>182467</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207183</t>
+          <t>207020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15171</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>184639</t>
+          <t>184736</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>223920</t>
+          <t>223533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,77%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>19142</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37663</t>
+          <t>37969</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>96476</t>
+          <t>97210</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109006</t>
+          <t>109005</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>115867</t>
+          <t>117099</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>146875</t>
+          <t>147841</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,83%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103428</t>
+          <t>103122</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122302</t>
+          <t>121949</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13742</t>
+          <t>13008</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>104433</t>
+          <t>103467</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>135441</t>
+          <t>134209</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,4%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87341</t>
+          <t>88479</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128270</t>
+          <t>128871</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>487602</t>
+          <t>486902</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>524709</t>
+          <t>525540</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>573623</t>
+          <t>573265</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>658317</t>
+          <t>654471</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1287242</t>
+          <t>1286641</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1328171</t>
+          <t>1327033</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>87367</t>
+          <t>86536</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>124474</t>
+          <t>125174</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1369271</t>
+          <t>1373117</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1453965</t>
+          <t>1454323</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>9343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32234</t>
+          <t>33035</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41397</t>
+          <t>41391</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13060</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29429</t>
+          <t>30359</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32050</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>131894</t>
+          <t>131752</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51818</t>
+          <t>50888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68187</t>
+          <t>68329</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185960</t>
+          <t>185712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204694</t>
+          <t>204696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18280</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32294</t>
+          <t>31517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>22524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>44919</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>248966</t>
+          <t>249055</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>261748</t>
+          <t>261476</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89733</t>
+          <t>90510</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107543</t>
+          <t>107405</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>345480</t>
+          <t>344443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>366870</t>
+          <t>366838</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>18128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45843</t>
+          <t>45915</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69891</t>
+          <t>71051</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53508</t>
+          <t>52908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86520</t>
+          <t>85248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251779</t>
+          <t>250701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>264214</t>
+          <t>264047</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62871</t>
+          <t>61711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86919</t>
+          <t>86847</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>315071</t>
+          <t>316343</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348083</t>
+          <t>348683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>16248</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36926</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>181543</t>
+          <t>181854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203450</t>
+          <t>205001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198221</t>
+          <t>194871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>242870</t>
+          <t>241032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>240005</t>
+          <t>240116</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>261609</t>
+          <t>260683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25419</t>
+          <t>23868</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47326</t>
+          <t>47015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>262931</t>
+          <t>264769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307580</t>
+          <t>310930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,47%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53311</t>
+          <t>52240</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81858</t>
+          <t>81453</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>178761</t>
+          <t>179484</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>191079</t>
+          <t>190980</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>232136</t>
+          <t>234029</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>274117</t>
+          <t>273304</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152075</t>
+          <t>152480</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180622</t>
+          <t>181693</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>153770</t>
+          <t>154583</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>195751</t>
+          <t>193858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47139</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73458</t>
+          <t>74082</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>136735</t>
+          <t>136787</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>183147</t>
+          <t>182277</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>217655</t>
+          <t>217445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,37%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93360</t>
+          <t>92736</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>119679</t>
+          <t>120222</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>91357</t>
+          <t>91567</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>125865</t>
+          <t>126735</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>148660</t>
+          <t>147863</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>199512</t>
+          <t>200353</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>595942</t>
+          <t>596811</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>654384</t>
+          <t>652904</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>753662</t>
+          <t>752333</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>847521</t>
+          <t>845417</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1175837</t>
+          <t>1174996</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1226689</t>
+          <t>1227486</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>264307</t>
+          <t>265787</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>322749</t>
+          <t>321880</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1446519</t>
+          <t>1448623</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1540378</t>
+          <t>1541707</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,2%</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>8948</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13952</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25443</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43218</t>
+          <t>43069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52725</t>
+          <t>52713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13857</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8613</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>143856</t>
+          <t>142876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154631</t>
+          <t>154343</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36928</t>
+          <t>36513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47370</t>
+          <t>47335</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>184900</t>
+          <t>184118</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199753</t>
+          <t>200116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19995</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30512</t>
+          <t>31564</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23446</t>
+          <t>23766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46059</t>
+          <t>46845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>230003</t>
+          <t>228906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244275</t>
+          <t>244267</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79579</t>
+          <t>78527</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95719</t>
+          <t>95666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314030</t>
+          <t>313244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>336643</t>
+          <t>336323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23033</t>
+          <t>24005</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29360</t>
+          <t>28592</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51271</t>
+          <t>50620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39089</t>
+          <t>40221</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67709</t>
+          <t>68191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>244427</t>
+          <t>243455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>260178</t>
+          <t>259308</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>86543</t>
+          <t>87194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108454</t>
+          <t>109222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337564</t>
+          <t>337082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366184</t>
+          <t>365052</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34829</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155496</t>
+          <t>154206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>180841</t>
+          <t>181358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170746</t>
+          <t>171039</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>213653</t>
+          <t>215633</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>233698</t>
+          <t>233865</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>253671</t>
+          <t>253806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>27586</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53448</t>
+          <t>54738</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>263817</t>
+          <t>261837</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>306724</t>
+          <t>306431</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,18%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54179</t>
+          <t>53875</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81351</t>
+          <t>79649</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>210655</t>
+          <t>211578</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>262114</t>
+          <t>262024</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>301939</t>
+          <t>302328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,23%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157436</t>
+          <t>159138</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>184608</t>
+          <t>184912</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>154569</t>
+          <t>154180</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>194394</t>
+          <t>194484</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35111</t>
+          <t>34726</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55244</t>
+          <t>54781</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>131455</t>
+          <t>131505</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>165618</t>
+          <t>165262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>198284</t>
+          <t>198357</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,77%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>97280</t>
+          <t>97743</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117413</t>
+          <t>117798</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94391</t>
+          <t>94318</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127057</t>
+          <t>127413</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>147024</t>
+          <t>146154</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194003</t>
+          <t>195350</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>564336</t>
+          <t>563374</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>621389</t>
+          <t>623986</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>720959</t>
+          <t>715239</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>811145</t>
+          <t>803734</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1163836</t>
+          <t>1162489</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1210815</t>
+          <t>1211685</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>275008</t>
+          <t>272411</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>332061</t>
+          <t>333023</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1443092</t>
+          <t>1450503</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1533278</t>
+          <t>1538998</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
